--- a/tests/fixtures/normal_workbook.xlsx
+++ b/tests/fixtures/normal_workbook.xlsx
@@ -10,21 +10,28 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HiddenSheet" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="DataStart">'Sheet1'!$A$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -123,6 +132,36 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>codex</author>
+  </authors>
+  <commentList>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>first row comment</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MainTable" displayName="MainTable" ref="A1:F121" headerRowCount="1">
+  <autoFilter ref="A1:F121"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="ID"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Value"/>
+    <tableColumn id="4" name="Created"/>
+    <tableColumn id="5" name="Formula"/>
+    <tableColumn id="6" name="Link"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -414,11 +453,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
@@ -431,6 +470,26 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Created</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Formula</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>MergedHeader</t>
         </is>
       </c>
     </row>
@@ -448,6 +507,18 @@
       <c r="C2" t="n">
         <v>1</v>
       </c>
+      <c r="D2" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E2">
+        <f>C2*2</f>
+        <v/>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://example.com/1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,6 +534,18 @@
       <c r="C3" t="n">
         <v>2</v>
       </c>
+      <c r="D3" s="2" t="n">
+        <v>46205</v>
+      </c>
+      <c r="E3">
+        <f>C3*2</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://example.com/2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -478,6 +561,18 @@
       <c r="C4" t="n">
         <v>3</v>
       </c>
+      <c r="D4" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E4">
+        <f>C4*2</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://example.com/3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -493,6 +588,18 @@
       <c r="C5" t="n">
         <v>4</v>
       </c>
+      <c r="D5" s="2" t="n">
+        <v>46207</v>
+      </c>
+      <c r="E5">
+        <f>C5*2</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://example.com/4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -508,6 +615,18 @@
       <c r="C6" t="n">
         <v>5</v>
       </c>
+      <c r="D6" s="2" t="n">
+        <v>46208</v>
+      </c>
+      <c r="E6">
+        <f>C6*2</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://example.com/5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -523,6 +642,18 @@
       <c r="C7" t="n">
         <v>6</v>
       </c>
+      <c r="D7" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="E7">
+        <f>C7*2</f>
+        <v/>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://example.com/6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -538,6 +669,18 @@
       <c r="C8" t="n">
         <v>7</v>
       </c>
+      <c r="D8" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="E8">
+        <f>C8*2</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://example.com/7</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -553,6 +696,18 @@
       <c r="C9" t="n">
         <v>8</v>
       </c>
+      <c r="D9" s="2" t="n">
+        <v>46211</v>
+      </c>
+      <c r="E9">
+        <f>C9*2</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://example.com/8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -568,6 +723,18 @@
       <c r="C10" t="n">
         <v>9</v>
       </c>
+      <c r="D10" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E10">
+        <f>C10*2</f>
+        <v/>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://example.com/9</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -583,6 +750,18 @@
       <c r="C11" t="n">
         <v>10</v>
       </c>
+      <c r="D11" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="E11">
+        <f>C11*2</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://example.com/10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -598,6 +777,18 @@
       <c r="C12" t="n">
         <v>11</v>
       </c>
+      <c r="D12" s="2" t="n">
+        <v>46214</v>
+      </c>
+      <c r="E12">
+        <f>C12*2</f>
+        <v/>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://example.com/11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -613,6 +804,18 @@
       <c r="C13" t="n">
         <v>12</v>
       </c>
+      <c r="D13" s="2" t="n">
+        <v>46215</v>
+      </c>
+      <c r="E13">
+        <f>C13*2</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://example.com/12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -628,6 +831,18 @@
       <c r="C14" t="n">
         <v>13</v>
       </c>
+      <c r="D14" s="2" t="n">
+        <v>46216</v>
+      </c>
+      <c r="E14">
+        <f>C14*2</f>
+        <v/>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://example.com/13</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -643,6 +858,18 @@
       <c r="C15" t="n">
         <v>14</v>
       </c>
+      <c r="D15" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="E15">
+        <f>C15*2</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://example.com/14</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -658,6 +885,18 @@
       <c r="C16" t="n">
         <v>15</v>
       </c>
+      <c r="D16" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E16">
+        <f>C16*2</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://example.com/15</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -673,6 +912,18 @@
       <c r="C17" t="n">
         <v>16</v>
       </c>
+      <c r="D17" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="E17">
+        <f>C17*2</f>
+        <v/>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://example.com/16</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -688,6 +939,18 @@
       <c r="C18" t="n">
         <v>17</v>
       </c>
+      <c r="D18" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="E18">
+        <f>C18*2</f>
+        <v/>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://example.com/17</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -703,6 +966,18 @@
       <c r="C19" t="n">
         <v>18</v>
       </c>
+      <c r="D19" s="2" t="n">
+        <v>46221</v>
+      </c>
+      <c r="E19">
+        <f>C19*2</f>
+        <v/>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://example.com/18</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -718,6 +993,18 @@
       <c r="C20" t="n">
         <v>19</v>
       </c>
+      <c r="D20" s="2" t="n">
+        <v>46222</v>
+      </c>
+      <c r="E20">
+        <f>C20*2</f>
+        <v/>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://example.com/19</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -733,6 +1020,18 @@
       <c r="C21" t="n">
         <v>20</v>
       </c>
+      <c r="D21" s="2" t="n">
+        <v>46223</v>
+      </c>
+      <c r="E21">
+        <f>C21*2</f>
+        <v/>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://example.com/20</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -748,6 +1047,18 @@
       <c r="C22" t="n">
         <v>21</v>
       </c>
+      <c r="D22" s="2" t="n">
+        <v>46224</v>
+      </c>
+      <c r="E22">
+        <f>C22*2</f>
+        <v/>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://example.com/21</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -763,6 +1074,18 @@
       <c r="C23" t="n">
         <v>22</v>
       </c>
+      <c r="D23" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="E23">
+        <f>C23*2</f>
+        <v/>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://example.com/22</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -778,6 +1101,18 @@
       <c r="C24" t="n">
         <v>23</v>
       </c>
+      <c r="D24" s="2" t="n">
+        <v>46226</v>
+      </c>
+      <c r="E24">
+        <f>C24*2</f>
+        <v/>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://example.com/23</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -793,6 +1128,18 @@
       <c r="C25" t="n">
         <v>24</v>
       </c>
+      <c r="D25" s="2" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E25">
+        <f>C25*2</f>
+        <v/>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://example.com/24</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -808,6 +1155,18 @@
       <c r="C26" t="n">
         <v>25</v>
       </c>
+      <c r="D26" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="E26">
+        <f>C26*2</f>
+        <v/>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://example.com/25</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -823,6 +1182,18 @@
       <c r="C27" t="n">
         <v>26</v>
       </c>
+      <c r="D27" s="2" t="n">
+        <v>46229</v>
+      </c>
+      <c r="E27">
+        <f>C27*2</f>
+        <v/>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://example.com/26</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -838,6 +1209,18 @@
       <c r="C28" t="n">
         <v>27</v>
       </c>
+      <c r="D28" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E28">
+        <f>C28*2</f>
+        <v/>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://example.com/27</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -853,6 +1236,18 @@
       <c r="C29" t="n">
         <v>28</v>
       </c>
+      <c r="D29" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E29">
+        <f>C29*2</f>
+        <v/>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://example.com/28</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -868,6 +1263,18 @@
       <c r="C30" t="n">
         <v>29</v>
       </c>
+      <c r="D30" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E30">
+        <f>C30*2</f>
+        <v/>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://example.com/29</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -883,6 +1290,18 @@
       <c r="C31" t="n">
         <v>30</v>
       </c>
+      <c r="D31" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E31">
+        <f>C31*2</f>
+        <v/>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://example.com/30</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -898,6 +1317,18 @@
       <c r="C32" t="n">
         <v>31</v>
       </c>
+      <c r="D32" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E32">
+        <f>C32*2</f>
+        <v/>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://example.com/31</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -913,6 +1344,18 @@
       <c r="C33" t="n">
         <v>32</v>
       </c>
+      <c r="D33" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E33">
+        <f>C33*2</f>
+        <v/>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://example.com/32</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -928,6 +1371,18 @@
       <c r="C34" t="n">
         <v>33</v>
       </c>
+      <c r="D34" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E34">
+        <f>C34*2</f>
+        <v/>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://example.com/33</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -943,6 +1398,18 @@
       <c r="C35" t="n">
         <v>34</v>
       </c>
+      <c r="D35" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E35">
+        <f>C35*2</f>
+        <v/>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://example.com/34</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -958,6 +1425,18 @@
       <c r="C36" t="n">
         <v>35</v>
       </c>
+      <c r="D36" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E36">
+        <f>C36*2</f>
+        <v/>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://example.com/35</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -973,6 +1452,18 @@
       <c r="C37" t="n">
         <v>36</v>
       </c>
+      <c r="D37" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E37">
+        <f>C37*2</f>
+        <v/>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://example.com/36</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -988,6 +1479,18 @@
       <c r="C38" t="n">
         <v>37</v>
       </c>
+      <c r="D38" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E38">
+        <f>C38*2</f>
+        <v/>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://example.com/37</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1003,6 +1506,18 @@
       <c r="C39" t="n">
         <v>38</v>
       </c>
+      <c r="D39" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E39">
+        <f>C39*2</f>
+        <v/>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://example.com/38</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1018,6 +1533,18 @@
       <c r="C40" t="n">
         <v>39</v>
       </c>
+      <c r="D40" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E40">
+        <f>C40*2</f>
+        <v/>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://example.com/39</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1033,6 +1560,18 @@
       <c r="C41" t="n">
         <v>40</v>
       </c>
+      <c r="D41" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E41">
+        <f>C41*2</f>
+        <v/>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://example.com/40</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1048,6 +1587,18 @@
       <c r="C42" t="n">
         <v>41</v>
       </c>
+      <c r="D42" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E42">
+        <f>C42*2</f>
+        <v/>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://example.com/41</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1063,6 +1614,18 @@
       <c r="C43" t="n">
         <v>42</v>
       </c>
+      <c r="D43" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E43">
+        <f>C43*2</f>
+        <v/>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://example.com/42</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1078,6 +1641,18 @@
       <c r="C44" t="n">
         <v>43</v>
       </c>
+      <c r="D44" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E44">
+        <f>C44*2</f>
+        <v/>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://example.com/43</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1093,6 +1668,18 @@
       <c r="C45" t="n">
         <v>44</v>
       </c>
+      <c r="D45" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E45">
+        <f>C45*2</f>
+        <v/>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://example.com/44</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1108,6 +1695,18 @@
       <c r="C46" t="n">
         <v>45</v>
       </c>
+      <c r="D46" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E46">
+        <f>C46*2</f>
+        <v/>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://example.com/45</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1123,6 +1722,18 @@
       <c r="C47" t="n">
         <v>46</v>
       </c>
+      <c r="D47" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E47">
+        <f>C47*2</f>
+        <v/>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://example.com/46</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1138,6 +1749,18 @@
       <c r="C48" t="n">
         <v>47</v>
       </c>
+      <c r="D48" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E48">
+        <f>C48*2</f>
+        <v/>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://example.com/47</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1153,6 +1776,18 @@
       <c r="C49" t="n">
         <v>48</v>
       </c>
+      <c r="D49" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E49">
+        <f>C49*2</f>
+        <v/>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://example.com/48</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1168,6 +1803,18 @@
       <c r="C50" t="n">
         <v>49</v>
       </c>
+      <c r="D50" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E50">
+        <f>C50*2</f>
+        <v/>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://example.com/49</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1183,6 +1830,18 @@
       <c r="C51" t="n">
         <v>50</v>
       </c>
+      <c r="D51" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E51">
+        <f>C51*2</f>
+        <v/>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://example.com/50</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1198,6 +1857,18 @@
       <c r="C52" t="n">
         <v>51</v>
       </c>
+      <c r="D52" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E52">
+        <f>C52*2</f>
+        <v/>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://example.com/51</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1213,6 +1884,18 @@
       <c r="C53" t="n">
         <v>52</v>
       </c>
+      <c r="D53" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E53">
+        <f>C53*2</f>
+        <v/>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://example.com/52</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1228,6 +1911,18 @@
       <c r="C54" t="n">
         <v>53</v>
       </c>
+      <c r="D54" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E54">
+        <f>C54*2</f>
+        <v/>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://example.com/53</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1243,6 +1938,18 @@
       <c r="C55" t="n">
         <v>54</v>
       </c>
+      <c r="D55" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E55">
+        <f>C55*2</f>
+        <v/>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://example.com/54</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1258,6 +1965,18 @@
       <c r="C56" t="n">
         <v>55</v>
       </c>
+      <c r="D56" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E56">
+        <f>C56*2</f>
+        <v/>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://example.com/55</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1273,6 +1992,18 @@
       <c r="C57" t="n">
         <v>56</v>
       </c>
+      <c r="D57" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E57">
+        <f>C57*2</f>
+        <v/>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://example.com/56</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1288,6 +2019,18 @@
       <c r="C58" t="n">
         <v>57</v>
       </c>
+      <c r="D58" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E58">
+        <f>C58*2</f>
+        <v/>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://example.com/57</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1303,6 +2046,18 @@
       <c r="C59" t="n">
         <v>58</v>
       </c>
+      <c r="D59" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E59">
+        <f>C59*2</f>
+        <v/>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://example.com/58</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1318,6 +2073,18 @@
       <c r="C60" t="n">
         <v>59</v>
       </c>
+      <c r="D60" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E60">
+        <f>C60*2</f>
+        <v/>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://example.com/59</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1333,6 +2100,18 @@
       <c r="C61" t="n">
         <v>60</v>
       </c>
+      <c r="D61" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E61">
+        <f>C61*2</f>
+        <v/>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://example.com/60</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1348,6 +2127,18 @@
       <c r="C62" t="n">
         <v>61</v>
       </c>
+      <c r="D62" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E62">
+        <f>C62*2</f>
+        <v/>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://example.com/61</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1363,6 +2154,18 @@
       <c r="C63" t="n">
         <v>62</v>
       </c>
+      <c r="D63" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E63">
+        <f>C63*2</f>
+        <v/>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://example.com/62</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1378,6 +2181,18 @@
       <c r="C64" t="n">
         <v>63</v>
       </c>
+      <c r="D64" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E64">
+        <f>C64*2</f>
+        <v/>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://example.com/63</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1393,6 +2208,18 @@
       <c r="C65" t="n">
         <v>64</v>
       </c>
+      <c r="D65" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E65">
+        <f>C65*2</f>
+        <v/>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://example.com/64</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1408,6 +2235,18 @@
       <c r="C66" t="n">
         <v>65</v>
       </c>
+      <c r="D66" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E66">
+        <f>C66*2</f>
+        <v/>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://example.com/65</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1423,6 +2262,18 @@
       <c r="C67" t="n">
         <v>66</v>
       </c>
+      <c r="D67" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E67">
+        <f>C67*2</f>
+        <v/>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://example.com/66</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1438,6 +2289,18 @@
       <c r="C68" t="n">
         <v>67</v>
       </c>
+      <c r="D68" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E68">
+        <f>C68*2</f>
+        <v/>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://example.com/67</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1453,6 +2316,18 @@
       <c r="C69" t="n">
         <v>68</v>
       </c>
+      <c r="D69" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E69">
+        <f>C69*2</f>
+        <v/>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://example.com/68</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1468,6 +2343,18 @@
       <c r="C70" t="n">
         <v>69</v>
       </c>
+      <c r="D70" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E70">
+        <f>C70*2</f>
+        <v/>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://example.com/69</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1483,6 +2370,18 @@
       <c r="C71" t="n">
         <v>70</v>
       </c>
+      <c r="D71" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E71">
+        <f>C71*2</f>
+        <v/>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://example.com/70</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1498,6 +2397,18 @@
       <c r="C72" t="n">
         <v>71</v>
       </c>
+      <c r="D72" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E72">
+        <f>C72*2</f>
+        <v/>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://example.com/71</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1513,6 +2424,18 @@
       <c r="C73" t="n">
         <v>72</v>
       </c>
+      <c r="D73" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E73">
+        <f>C73*2</f>
+        <v/>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://example.com/72</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1528,6 +2451,18 @@
       <c r="C74" t="n">
         <v>73</v>
       </c>
+      <c r="D74" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E74">
+        <f>C74*2</f>
+        <v/>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://example.com/73</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1543,6 +2478,18 @@
       <c r="C75" t="n">
         <v>74</v>
       </c>
+      <c r="D75" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E75">
+        <f>C75*2</f>
+        <v/>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://example.com/74</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1558,6 +2505,18 @@
       <c r="C76" t="n">
         <v>75</v>
       </c>
+      <c r="D76" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E76">
+        <f>C76*2</f>
+        <v/>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://example.com/75</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1573,6 +2532,18 @@
       <c r="C77" t="n">
         <v>76</v>
       </c>
+      <c r="D77" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E77">
+        <f>C77*2</f>
+        <v/>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://example.com/76</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1588,6 +2559,18 @@
       <c r="C78" t="n">
         <v>77</v>
       </c>
+      <c r="D78" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E78">
+        <f>C78*2</f>
+        <v/>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://example.com/77</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1603,6 +2586,18 @@
       <c r="C79" t="n">
         <v>78</v>
       </c>
+      <c r="D79" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E79">
+        <f>C79*2</f>
+        <v/>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://example.com/78</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1618,6 +2613,18 @@
       <c r="C80" t="n">
         <v>79</v>
       </c>
+      <c r="D80" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E80">
+        <f>C80*2</f>
+        <v/>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://example.com/79</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1633,6 +2640,18 @@
       <c r="C81" t="n">
         <v>80</v>
       </c>
+      <c r="D81" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E81">
+        <f>C81*2</f>
+        <v/>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://example.com/80</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1648,6 +2667,18 @@
       <c r="C82" t="n">
         <v>81</v>
       </c>
+      <c r="D82" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E82">
+        <f>C82*2</f>
+        <v/>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://example.com/81</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1663,6 +2694,18 @@
       <c r="C83" t="n">
         <v>82</v>
       </c>
+      <c r="D83" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E83">
+        <f>C83*2</f>
+        <v/>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://example.com/82</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1678,6 +2721,18 @@
       <c r="C84" t="n">
         <v>83</v>
       </c>
+      <c r="D84" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E84">
+        <f>C84*2</f>
+        <v/>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://example.com/83</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1693,6 +2748,18 @@
       <c r="C85" t="n">
         <v>84</v>
       </c>
+      <c r="D85" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E85">
+        <f>C85*2</f>
+        <v/>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://example.com/84</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1708,6 +2775,18 @@
       <c r="C86" t="n">
         <v>85</v>
       </c>
+      <c r="D86" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E86">
+        <f>C86*2</f>
+        <v/>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://example.com/85</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1723,6 +2802,18 @@
       <c r="C87" t="n">
         <v>86</v>
       </c>
+      <c r="D87" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E87">
+        <f>C87*2</f>
+        <v/>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://example.com/86</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1738,6 +2829,18 @@
       <c r="C88" t="n">
         <v>87</v>
       </c>
+      <c r="D88" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E88">
+        <f>C88*2</f>
+        <v/>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://example.com/87</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1753,6 +2856,18 @@
       <c r="C89" t="n">
         <v>88</v>
       </c>
+      <c r="D89" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E89">
+        <f>C89*2</f>
+        <v/>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://example.com/88</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1768,6 +2883,18 @@
       <c r="C90" t="n">
         <v>89</v>
       </c>
+      <c r="D90" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E90">
+        <f>C90*2</f>
+        <v/>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://example.com/89</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1783,6 +2910,18 @@
       <c r="C91" t="n">
         <v>90</v>
       </c>
+      <c r="D91" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E91">
+        <f>C91*2</f>
+        <v/>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://example.com/90</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1798,6 +2937,18 @@
       <c r="C92" t="n">
         <v>91</v>
       </c>
+      <c r="D92" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E92">
+        <f>C92*2</f>
+        <v/>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://example.com/91</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1813,6 +2964,18 @@
       <c r="C93" t="n">
         <v>92</v>
       </c>
+      <c r="D93" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E93">
+        <f>C93*2</f>
+        <v/>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://example.com/92</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1828,6 +2991,18 @@
       <c r="C94" t="n">
         <v>93</v>
       </c>
+      <c r="D94" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E94">
+        <f>C94*2</f>
+        <v/>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://example.com/93</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1843,6 +3018,18 @@
       <c r="C95" t="n">
         <v>94</v>
       </c>
+      <c r="D95" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E95">
+        <f>C95*2</f>
+        <v/>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://example.com/94</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1858,6 +3045,18 @@
       <c r="C96" t="n">
         <v>95</v>
       </c>
+      <c r="D96" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E96">
+        <f>C96*2</f>
+        <v/>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://example.com/95</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1873,6 +3072,18 @@
       <c r="C97" t="n">
         <v>96</v>
       </c>
+      <c r="D97" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E97">
+        <f>C97*2</f>
+        <v/>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://example.com/96</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1888,6 +3099,18 @@
       <c r="C98" t="n">
         <v>97</v>
       </c>
+      <c r="D98" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E98">
+        <f>C98*2</f>
+        <v/>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://example.com/97</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1903,6 +3126,18 @@
       <c r="C99" t="n">
         <v>98</v>
       </c>
+      <c r="D99" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E99">
+        <f>C99*2</f>
+        <v/>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://example.com/98</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1918,6 +3153,18 @@
       <c r="C100" t="n">
         <v>99</v>
       </c>
+      <c r="D100" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E100">
+        <f>C100*2</f>
+        <v/>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://example.com/99</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1933,6 +3180,18 @@
       <c r="C101" t="n">
         <v>100</v>
       </c>
+      <c r="D101" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E101">
+        <f>C101*2</f>
+        <v/>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://example.com/100</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1948,6 +3207,18 @@
       <c r="C102" t="n">
         <v>101</v>
       </c>
+      <c r="D102" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E102">
+        <f>C102*2</f>
+        <v/>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://example.com/101</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1963,6 +3234,18 @@
       <c r="C103" t="n">
         <v>102</v>
       </c>
+      <c r="D103" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E103">
+        <f>C103*2</f>
+        <v/>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://example.com/102</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1978,6 +3261,18 @@
       <c r="C104" t="n">
         <v>103</v>
       </c>
+      <c r="D104" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E104">
+        <f>C104*2</f>
+        <v/>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://example.com/103</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1993,6 +3288,18 @@
       <c r="C105" t="n">
         <v>104</v>
       </c>
+      <c r="D105" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E105">
+        <f>C105*2</f>
+        <v/>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://example.com/104</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2008,6 +3315,18 @@
       <c r="C106" t="n">
         <v>105</v>
       </c>
+      <c r="D106" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E106">
+        <f>C106*2</f>
+        <v/>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://example.com/105</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2023,6 +3342,18 @@
       <c r="C107" t="n">
         <v>106</v>
       </c>
+      <c r="D107" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E107">
+        <f>C107*2</f>
+        <v/>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://example.com/106</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2038,6 +3369,18 @@
       <c r="C108" t="n">
         <v>107</v>
       </c>
+      <c r="D108" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E108">
+        <f>C108*2</f>
+        <v/>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://example.com/107</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2053,6 +3396,18 @@
       <c r="C109" t="n">
         <v>108</v>
       </c>
+      <c r="D109" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E109">
+        <f>C109*2</f>
+        <v/>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://example.com/108</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2068,6 +3423,18 @@
       <c r="C110" t="n">
         <v>109</v>
       </c>
+      <c r="D110" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E110">
+        <f>C110*2</f>
+        <v/>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://example.com/109</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2083,6 +3450,18 @@
       <c r="C111" t="n">
         <v>110</v>
       </c>
+      <c r="D111" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E111">
+        <f>C111*2</f>
+        <v/>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://example.com/110</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2098,6 +3477,18 @@
       <c r="C112" t="n">
         <v>111</v>
       </c>
+      <c r="D112" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E112">
+        <f>C112*2</f>
+        <v/>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://example.com/111</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2113,6 +3504,18 @@
       <c r="C113" t="n">
         <v>112</v>
       </c>
+      <c r="D113" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E113">
+        <f>C113*2</f>
+        <v/>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://example.com/112</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2128,6 +3531,18 @@
       <c r="C114" t="n">
         <v>113</v>
       </c>
+      <c r="D114" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E114">
+        <f>C114*2</f>
+        <v/>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://example.com/113</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2143,6 +3558,18 @@
       <c r="C115" t="n">
         <v>114</v>
       </c>
+      <c r="D115" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E115">
+        <f>C115*2</f>
+        <v/>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://example.com/114</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2158,6 +3585,18 @@
       <c r="C116" t="n">
         <v>115</v>
       </c>
+      <c r="D116" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E116">
+        <f>C116*2</f>
+        <v/>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://example.com/115</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2173,6 +3612,18 @@
       <c r="C117" t="n">
         <v>116</v>
       </c>
+      <c r="D117" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E117">
+        <f>C117*2</f>
+        <v/>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://example.com/116</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2188,6 +3639,18 @@
       <c r="C118" t="n">
         <v>117</v>
       </c>
+      <c r="D118" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E118">
+        <f>C118*2</f>
+        <v/>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://example.com/117</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2203,6 +3666,18 @@
       <c r="C119" t="n">
         <v>118</v>
       </c>
+      <c r="D119" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E119">
+        <f>C119*2</f>
+        <v/>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://example.com/118</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2218,6 +3693,18 @@
       <c r="C120" t="n">
         <v>119</v>
       </c>
+      <c r="D120" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E120">
+        <f>C120*2</f>
+        <v/>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://example.com/119</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2233,9 +3720,31 @@
       <c r="C121" t="n">
         <v>120</v>
       </c>
+      <c r="D121" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="E121">
+        <f>C121*2</f>
+        <v/>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://example.com/120</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:I1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
